--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/المحاسبة_طالبات.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/المحاسبة_طالبات.xlsx
@@ -461,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>ريم احمد محمد علي</v>
+        <v>السارة سعد علي احمد</v>
       </c>
       <c r="C4" t="str">
         <v>208</v>
@@ -501,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>ريم احمد محمد علي</v>
+        <v>رانيا سلطان محمد عبدالحميد</v>
       </c>
       <c r="C6" t="str">
         <v>208</v>
@@ -541,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>اميره سالم غانم اليحيوي</v>
+        <v>نوير منير جميل القثامي</v>
       </c>
       <c r="C8" t="str">
         <v>207</v>
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>نوال محمد عايش الجعيد</v>
+        <v>هند عبدالرازق مرزوق الطلحي</v>
       </c>
       <c r="C9" t="str">
         <v>206</v>
@@ -621,7 +621,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>امنة محمد امين عبدالكريم امين بخاري</v>
+        <v>درية بله احمد مهدي</v>
       </c>
       <c r="C12" t="str">
         <v>211</v>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>اميره سالم غانم اليحيوي</v>
+        <v>منال محمد سالم العيدروس</v>
       </c>
       <c r="C14" t="str">
         <v>207</v>
